--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484572_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484572_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>G. VOLPATO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5511</v>
+        <v>3.7476</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8436</v>
+        <v>2.3857</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7075</v>
+        <v>1.3619</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6927</v>
+        <v>2.9503</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1473</v>
+        <v>0.8338</v>
       </c>
       <c r="I2" t="n">
-        <v>1.84</v>
+        <v>2.1164</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1893</v>
+        <v>2.4743</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3625</v>
+        <v>1.1271</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5518</v>
+        <v>1.3472</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4965</v>
+        <v>0.476</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.2932</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2882</v>
+        <v>0.7692</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6493</v>
+        <v>1.8326</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5656</v>
+        <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0788</v>
+        <v>-1.0353</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.0886</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6384</v>
+        <v>-0.9467</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2878</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2878</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. VOLPATO</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3294</v>
+        <v>3.0582</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2895</v>
+        <v>0.9948</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0399</v>
+        <v>2.0634</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9503</v>
+        <v>0.6927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8338</v>
+        <v>-1.1473</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1164</v>
+        <v>1.84</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4743</v>
+        <v>1.1893</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1271</v>
+        <v>-0.3625</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3472</v>
+        <v>1.5518</v>
       </c>
       <c r="M3" t="n">
-        <v>0.476</v>
+        <v>-0.4965</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2932</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7692</v>
+        <v>0.2882</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8326</v>
+        <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4535</v>
+        <v>-0.5717</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1847</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2687</v>
+        <v>-0.0057</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2878</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2878</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9826</v>
+        <v>1.5436</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3024</v>
+        <v>1.5908</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3198</v>
+        <v>-0.0473</v>
       </c>
       <c r="G4" t="n">
         <v>3.4138</v>
@@ -766,13 +766,13 @@
         <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8998</v>
+        <v>-0.3388</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3673</v>
+        <v>-0.0788</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5325</v>
+        <v>-0.26</v>
       </c>
       <c r="V4" t="n">
         <v>0.3011</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.16</v>
+        <v>0.0196</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8222</v>
+        <v>-1.4923</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6622</v>
+        <v>1.5119</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0252</v>
+        <v>-1.5843</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3519</v>
+        <v>-1.0044</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6733</v>
+        <v>-0.58</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1322</v>
+        <v>-0.737</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7153</v>
+        <v>0.4519</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4169</v>
+        <v>-1.1889</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1069</v>
+        <v>-0.8474</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3633</v>
+        <v>-1.4563</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2564</v>
+        <v>0.6089</v>
       </c>
       <c r="P5" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.9163</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.8326</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.9163</v>
+        <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0039</v>
+        <v>-0.4583</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2006</v>
+        <v>-0.7945</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2045</v>
+        <v>0.3361</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.945</v>
+        <v>1.3293</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>0.9554</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.267</v>
+        <v>0.3738</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2496</v>
+        <v>0.0172</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8358</v>
+        <v>0.6299</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5863</v>
+        <v>-0.6126</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5843</v>
+        <v>2.0252</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0044</v>
+        <v>0.3519</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.58</v>
+        <v>1.6733</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.737</v>
+        <v>2.1322</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4519</v>
+        <v>0.7153</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1889</v>
+        <v>1.4169</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8474</v>
+        <v>-0.1069</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4563</v>
+        <v>-0.3633</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6089</v>
+        <v>0.2564</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7275</v>
+        <v>-0.1467</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.138</v>
+        <v>0.0083</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4105</v>
+        <v>-0.155</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3293</v>
+        <v>-0.945</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9554</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3738</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7551</v>
+        <v>-0.9999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.9262</v>
       </c>
       <c r="F7" t="n">
-        <v>0.075</v>
+        <v>-0.0737</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0381</v>
@@ -1000,13 +1000,13 @@
         <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4876</v>
+        <v>0.2428</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2738</v>
+        <v>0.1776</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2139</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2047</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8932</v>
+        <v>-1.6675</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5593</v>
+        <v>-2.7648</v>
       </c>
       <c r="F8" t="n">
-        <v>1.666</v>
+        <v>1.0973</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4053</v>
+        <v>-2.3442</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.091</v>
+        <v>0.0789</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3143</v>
+        <v>-2.4232</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4844</v>
+        <v>-1.6005</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0101</v>
+        <v>0.8545</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4743</v>
+        <v>-2.455</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9208</v>
+        <v>-0.7437</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0808</v>
+        <v>-0.7756</v>
       </c>
       <c r="O8" t="n">
-        <v>0.16</v>
+        <v>0.0318</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.733</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4839</v>
+        <v>0.1146</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9752</v>
+        <v>-0.3367</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5087</v>
+        <v>0.4513</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2388</v>
+        <v>1.6616</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3011</v>
+        <v>1.9213</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0623</v>
+        <v>-0.2596</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1367</v>
+        <v>-1.6778</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4145</v>
+        <v>-0.0299</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7222</v>
+        <v>-1.6479</v>
       </c>
       <c r="G9" t="n">
         <v>0.6304</v>
@@ -1156,13 +1156,13 @@
         <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8117</v>
+        <v>-0.3528</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2753</v>
+        <v>0.1094</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5364</v>
+        <v>-0.4621</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5889</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3461</v>
+        <v>-2.4754</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4929</v>
+        <v>-2.7502</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1468</v>
+        <v>0.2748</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3442</v>
+        <v>-2.9198</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0789</v>
+        <v>-0.7756</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4232</v>
+        <v>-2.1442</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6005</v>
+        <v>-1.4372</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8545</v>
+        <v>0.867</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.455</v>
+        <v>-2.3042</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7437</v>
+        <v>-1.4825</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7756</v>
+        <v>-1.6425</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0318</v>
+        <v>0.16</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6493</v>
+        <v>2.5656</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.3118</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0648</v>
+        <v>-0.3966</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5009</v>
+        <v>0.0848</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6616</v>
+        <v>-0.8931</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9213</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2596</v>
+        <v>-0.8931</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0696</v>
+        <v>-2.7176</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9975</v>
+        <v>-4.235</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07199999999999999</v>
+        <v>1.5174</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9198</v>
+        <v>-2.4053</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7756</v>
+        <v>-2.091</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1442</v>
+        <v>-0.3143</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4372</v>
+        <v>-1.4844</v>
       </c>
       <c r="K11" t="n">
-        <v>0.867</v>
+        <v>-1.0101</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.3042</v>
+        <v>-0.4743</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4825</v>
+        <v>-0.9208</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6425</v>
+        <v>-1.0808</v>
       </c>
       <c r="O11" t="n">
         <v>0.16</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6493</v>
+        <v>-0.733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5656</v>
+        <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.906</v>
+        <v>0.6595</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.644</v>
+        <v>0.2994</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.262</v>
+        <v>0.3601</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8931</v>
+        <v>-0.2388</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8931</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4272</v>
+        <v>-1.152000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8724</v>
+        <v>-6.597200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.4453</v>
+        <v>5.4452</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4207000000000005</v>
+        <v>0.4207000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>-2.3057</v>
@@ -1366,10 +1366,10 @@
         <v>4.277699999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2747</v>
+        <v>4.274699999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003000000000000114</v>
+        <v>0.003000000000000058</v>
       </c>
       <c r="M12" t="n">
         <v>-3.8566</v>
@@ -1381,7 +1381,7 @@
         <v>2.723</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9163000000000002</v>
+        <v>0.9163</v>
       </c>
       <c r="Q12" t="n">
         <v>-14.6608</v>
@@ -1390,22 +1390,22 @@
         <v>15.5769</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4737</v>
+        <v>-2.1985</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9417</v>
+        <v>-1.6665</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5317</v>
+        <v>-0.5320000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2907000000000002</v>
+        <v>-0.2907000000000003</v>
       </c>
       <c r="W12" t="n">
         <v>5.4523</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.743</v>
+        <v>-5.742999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.2838</v>
+        <v>6.9138</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5671</v>
+        <v>3.9902</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7167</v>
+        <v>2.9236</v>
       </c>
       <c r="G13" t="n">
         <v>4.1652</v>
@@ -1468,13 +1468,13 @@
         <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5243</v>
+        <v>1.1542</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1516</v>
+        <v>0.5747</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3727</v>
+        <v>0.5795</v>
       </c>
       <c r="V13" t="n">
         <v>0.3115</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6422</v>
+        <v>3.7262</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5254</v>
+        <v>2.0061</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1168</v>
+        <v>1.72</v>
       </c>
       <c r="G14" t="n">
         <v>3.3644</v>
@@ -1546,13 +1546,13 @@
         <v>2.0158</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7039</v>
+        <v>0.3801</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2586</v>
+        <v>0.2221</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4453</v>
+        <v>0.158</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9346</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9693</v>
+        <v>1.5847</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4921</v>
+        <v>1.1074</v>
       </c>
       <c r="F15" t="n">
         <v>0.4772</v>
@@ -1624,10 +1624,10 @@
         <v>0.5498</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5679</v>
+        <v>0.1833</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4208</v>
+        <v>0.0362</v>
       </c>
       <c r="U15" t="n">
         <v>0.1471</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8037</v>
+        <v>0.6353</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3839</v>
+        <v>-0.2349</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4198</v>
+        <v>0.8703</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3038</v>
+        <v>-0.2501</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4349</v>
+        <v>-0.4423</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1311</v>
+        <v>0.1922</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4294</v>
+        <v>-0.1675</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3619</v>
+        <v>-0.1675</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7332</v>
+        <v>-0.0827</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7968</v>
+        <v>-0.2748</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.1922</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1991</v>
+        <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2254</v>
+        <v>-0.0596</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0046</v>
+        <v>-0.4182</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2209</v>
+        <v>0.3586</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3011</v>
+        <v>0.945</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9658</v>
+        <v>1.267</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>D. MUÑOZ TORREGROSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5887</v>
+        <v>0.3251</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3311</v>
+        <v>0.3251</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9198</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2501</v>
+        <v>0.3251</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4423</v>
+        <v>0.3251</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1922</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1675</v>
+        <v>0.3251</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1675</v>
+        <v>0.3251</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0827</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2748</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1922</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1062</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5143</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4081</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MUÑOZ TORREGROSA</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3251</v>
+        <v>0.2602</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3251</v>
+        <v>-0.193</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.4532</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3251</v>
+        <v>-0.3038</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3251</v>
+        <v>-0.4349</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.1311</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3251</v>
+        <v>0.4294</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3251</v>
+        <v>0.3619</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.7332</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.7968</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.6819</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.4276</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2543</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.9658</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0309</v>
+        <v>0.1396</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1758</v>
+        <v>-1.0796</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1449</v>
+        <v>1.2192</v>
       </c>
       <c r="G20" t="n">
         <v>0.9088000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.1833</v>
       </c>
       <c r="S20" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.257</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1652</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2517</v>
+        <v>0.326</v>
       </c>
       <c r="V20" t="n">
         <v>0.6231</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7174</v>
+        <v>-0.7378</v>
       </c>
       <c r="E21" t="n">
         <v>-0.9657</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2484</v>
+        <v>0.2279</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0845</v>
@@ -2092,13 +2092,13 @@
         <v>2.1991</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2938</v>
+        <v>1.2734</v>
       </c>
       <c r="T21" t="n">
         <v>0.5837</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7101</v>
+        <v>0.6896</v>
       </c>
       <c r="V21" t="n">
         <v>1.89</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0934</v>
+        <v>-0.8195</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.637</v>
+        <v>-1.5408</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5436</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0.7612</v>
@@ -2170,13 +2170,13 @@
         <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.755</v>
+        <v>-0.4811</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5505</v>
+        <v>-0.4544</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2045</v>
+        <v>-0.0268</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9732</v>
+        <v>-1.6323</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7402</v>
+        <v>-1.5479</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.233</v>
+        <v>-0.0843</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5302</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.3299</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5324</v>
+        <v>-0.3401</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1385</v>
+        <v>0.0102</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3219</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8152</v>
+        <v>-2.078</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6324</v>
+        <v>-3.1516</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8171</v>
+        <v>1.0736</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2346</v>
@@ -2326,13 +2326,13 @@
         <v>2.3823</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0362</v>
+        <v>0.701</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3137</v>
+        <v>0.1671</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2775</v>
+        <v>0.5339</v>
       </c>
       <c r="V24" t="n">
         <v>-1.9109</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.856</v>
+        <v>-6.9084</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.5571</v>
+        <v>-5.461</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2988</v>
+        <v>-1.4475</v>
       </c>
       <c r="G25" t="n">
         <v>-4.7048</v>
@@ -2404,13 +2404,13 @@
         <v>0.5498</v>
       </c>
       <c r="S25" t="n">
-        <v>0.048</v>
+        <v>-0.0045</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2941</v>
+        <v>-0.198</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3421</v>
+        <v>0.1934</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.427200000000001</v>
+        <v>2.7094</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.4452</v>
+        <v>-5.445200000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>6.8725</v>
+        <v>8.154500000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-0.4208000000000007</v>
@@ -2482,13 +2482,13 @@
         <v>14.6606</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4737</v>
+        <v>3.7558</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5319</v>
+        <v>0.5317000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>1.9419</v>
+        <v>3.2238</v>
       </c>
       <c r="V26" t="n">
         <v>0.2907</v>
